--- a/branches/review/2027.0.0-ballot2-en/ValueSet-mii-vs-mikrobio-susceptibility-norm.xlsx
+++ b/branches/review/2027.0.0-ballot2-en/ValueSet-mii-vs-mikrobio-susceptibility-norm.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T01:04:27+00:00</t>
+    <t>2026-10-19T02:33:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Norm ValueSet for susceptibility testing: the norm system on whose breakpoints a category is based. Bound to the extension MII_EX_Mikrobio_Empfindlichkeit_Norm.</t>
+    <t>Norm ValueSet for susceptibility testing: the interpretive standard (e.g. EUCAST, CLSI) on whose breakpoints a category is based. Bound to the extension MII_EX_Mikrobio_Empfindlichkeit_Norm.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/branches/review/2027.0.0-ballot2-en/ValueSet-mii-vs-mikrobio-susceptibility-norm.xlsx
+++ b/branches/review/2027.0.0-ballot2-en/ValueSet-mii-vs-mikrobio-susceptibility-norm.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T02:33:36+00:00</t>
+    <t>2026-10-19T02:49:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
